--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -12753,6 +12753,408 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Japan NIID Kyasanur Forest disease notifications; corrects the former source-label typo Casanul forest disease.</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN63" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12786,7 +13188,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -12869,7 +13271,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -12879,7 +13281,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -12899,7 +13301,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -768,9 +768,6 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1020,7 +1017,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1170,9 +1167,6 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1422,7 +1416,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1572,9 +1566,6 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1824,7 +1815,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1974,9 +1965,6 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2226,7 +2214,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2376,9 +2364,6 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2628,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2778,9 +2763,6 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3030,7 +3012,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3180,9 +3162,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3432,7 +3411,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3582,9 +3561,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3834,7 +3810,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3984,9 +3960,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4236,7 +4209,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4386,9 +4359,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4638,7 +4608,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4788,9 +4758,6 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5040,7 +5007,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5190,9 +5157,6 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5442,7 +5406,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5592,9 +5556,6 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5844,7 +5805,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5994,9 +5955,6 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6246,7 +6204,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6396,9 +6354,6 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6648,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6798,9 +6753,6 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -7050,7 +7002,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7200,9 +7152,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7452,7 +7401,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7602,9 +7551,6 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7854,7 +7800,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8004,9 +7950,6 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8256,7 +8199,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8406,9 +8349,6 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8658,7 +8598,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8808,9 +8748,6 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -9060,7 +8997,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9210,9 +9147,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9462,7 +9396,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9612,9 +9546,6 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9864,7 +9795,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10014,9 +9945,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10266,7 +10194,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10416,9 +10344,6 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10668,7 +10593,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10818,9 +10743,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -11070,7 +10992,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11220,9 +11142,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -11472,7 +11391,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,9 +11541,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11874,7 +11790,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12024,9 +11940,6 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -12276,7 +12189,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12426,9 +12339,6 @@
       <c r="P60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12678,7 +12588,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12828,9 +12738,6 @@
       <c r="P62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -13080,7 +12987,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -13062,6 +13062,405 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Japan NIID Kyasanur Forest disease notifications; corrects the former source-label typo Casanul forest disease.</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN65" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13095,7 +13494,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13577,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -13188,7 +13587,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -13208,7 +13607,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -13461,6 +13461,405 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Japan NIID Kyasanur Forest disease notifications; corrects the former source-label typo Casanul forest disease.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13494,7 +13893,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13577,7 +13976,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -13587,7 +13986,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -13607,7 +14006,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d217/2026-2029.xlsx
+++ b/diseases/d217/2026-2029.xlsx
@@ -13860,6 +13860,405 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>kyasanur-forest-disease</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D217</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>基亚萨努尔森林病</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Kyasanur Forest disease</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Japan NIID Kyasanur Forest disease notifications; corrects the former source-label typo Casanul forest disease.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_JP_KYASANUR_FOREST_DISEASE_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13893,7 +14292,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -13976,7 +14375,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -13986,7 +14385,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -14006,7 +14405,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
